--- a/Data/Excel/skill_action.xlsx
+++ b/Data/Excel/skill_action.xlsx
@@ -111,49 +111,49 @@
     <t>sound asset location</t>
   </si>
   <si>
-    <t>Effect/FireballHit</t>
-  </si>
-  <si>
-    <t>Sound/Fireball</t>
-  </si>
-  <si>
-    <t>Effect/FrostNova</t>
-  </si>
-  <si>
-    <t>Sound/FrostNova</t>
-  </si>
-  <si>
-    <t>Effect/FrostSlow</t>
-  </si>
-  <si>
-    <t>Effect/IceHit</t>
-  </si>
-  <si>
-    <t>Effect/IceSlow</t>
-  </si>
-  <si>
-    <t>Effect/Heal</t>
-  </si>
-  <si>
-    <t>Sound/Heal</t>
-  </si>
-  <si>
-    <t>Effect/PoisonCloud</t>
-  </si>
-  <si>
-    <t>Sound/Poison</t>
-  </si>
-  <si>
-    <t>Effect/StunBolt</t>
-  </si>
-  <si>
-    <t>Sound/Lightning</t>
-  </si>
-  <si>
-    <t>Effect/Stun</t>
-  </si>
-  <si>
-    <t>Effect/AuraAttackSpeed</t>
+    <t>Assets/Arts/Effects/BowHitEffect.prefab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
+  </si>
+  <si>
+    <t>Assets/Arts/Effects/IceHitEffect.prefab</t>
   </si>
 </sst>
 </file>

--- a/Data/Excel/skill_action.xlsx
+++ b/Data/Excel/skill_action.xlsx
@@ -573,10 +573,10 @@
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="B5" s="4">
-        <v>1</v>
+        <v>50210001</v>
       </c>
       <c r="C5" s="2">
-        <v>1001</v>
+        <v>50200001</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -611,10 +611,10 @@
     </row>
     <row r="6" spans="1:13" ht="15" customHeight="1">
       <c r="B6" s="4">
-        <v>2</v>
+        <v>50210002</v>
       </c>
       <c r="C6" s="2">
-        <v>1002</v>
+        <v>50200002</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -649,10 +649,10 @@
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="B7" s="4">
-        <v>3</v>
+        <v>50210003</v>
       </c>
       <c r="C7" s="2">
-        <v>1002</v>
+        <v>50200002</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -673,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="2">
-        <v>3001</v>
+        <v>50500001</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
@@ -685,10 +685,10 @@
     </row>
     <row r="8" spans="1:13" ht="15" customHeight="1">
       <c r="B8" s="4">
-        <v>4</v>
+        <v>50210004</v>
       </c>
       <c r="C8" s="2">
-        <v>1003</v>
+        <v>50200003</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -721,10 +721,10 @@
     </row>
     <row r="9" spans="1:13" ht="15" customHeight="1">
       <c r="B9" s="4">
-        <v>5</v>
+        <v>50210005</v>
       </c>
       <c r="C9" s="2">
-        <v>1003</v>
+        <v>50200003</v>
       </c>
       <c r="D9" s="2">
         <v>2</v>
@@ -745,7 +745,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="2">
-        <v>3002</v>
+        <v>50500002</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
@@ -757,10 +757,10 @@
     </row>
     <row r="10" spans="1:13" ht="15" customHeight="1">
       <c r="B10" s="4">
-        <v>6</v>
+        <v>50210006</v>
       </c>
       <c r="C10" s="2">
-        <v>1004</v>
+        <v>50200004</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="11" spans="1:13" ht="15" customHeight="1">
       <c r="B11" s="4">
-        <v>7</v>
+        <v>50210007</v>
       </c>
       <c r="C11" s="2">
-        <v>1005</v>
+        <v>50200005</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -819,7 +819,7 @@
         <v>6</v>
       </c>
       <c r="J11" s="2">
-        <v>3004</v>
+        <v>50500004</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
@@ -833,10 +833,10 @@
     </row>
     <row r="12" spans="1:13" ht="15" customHeight="1">
       <c r="B12" s="4">
-        <v>8</v>
+        <v>50210008</v>
       </c>
       <c r="C12" s="2">
-        <v>1006</v>
+        <v>50200006</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -871,10 +871,10 @@
     </row>
     <row r="13" spans="1:13" ht="15" customHeight="1">
       <c r="B13" s="4">
-        <v>9</v>
+        <v>50210009</v>
       </c>
       <c r="C13" s="2">
-        <v>1006</v>
+        <v>50200006</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -895,7 +895,7 @@
         <v>1.5</v>
       </c>
       <c r="J13" s="2">
-        <v>3005</v>
+        <v>50500005</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="14" spans="1:13" ht="15" customHeight="1">
       <c r="B14" s="4">
-        <v>10</v>
+        <v>50210010</v>
       </c>
       <c r="C14" s="2">
-        <v>2001</v>
+        <v>50201001</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -931,7 +931,7 @@
         <v>-1</v>
       </c>
       <c r="J14" s="2">
-        <v>3003</v>
+        <v>50500003</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
